--- a/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-701_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO LA GIRALDA (IED)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-701_CALIFICADO.xlsx
@@ -858,9 +858,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1609,9 +1609,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2316,9 +2316,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3573,9 +3573,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3826,9 +3826,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4549,9 +4549,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4802,9 +4802,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -5300,9 +5300,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5553,9 +5553,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -6055,9 +6055,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6814,9 +6814,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -7316,9 +7316,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -7569,9 +7569,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -7822,9 +7822,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -8075,9 +8075,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -8581,9 +8581,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -8834,9 +8834,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -9846,9 +9846,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10099,9 +10099,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1305,11 +1297,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1317,7 +1305,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1558,11 +1546,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1570,7 +1554,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1799,11 +1783,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1811,7 +1791,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2036,11 +2016,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2048,7 +2024,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2265,11 +2241,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2277,7 +2249,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2518,11 +2490,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2530,7 +2498,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2771,11 +2739,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2783,7 +2747,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3024,11 +2988,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3036,7 +2996,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3269,11 +3229,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3281,7 +3237,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3522,11 +3478,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3534,7 +3486,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3775,11 +3727,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3787,7 +3735,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4028,11 +3976,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4040,7 +3984,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4269,11 +4213,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4281,7 +4221,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4498,11 +4438,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4510,7 +4446,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4751,11 +4687,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4763,7 +4695,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5004,11 +4936,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5016,7 +4944,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5249,11 +5177,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5261,7 +5185,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5502,11 +5426,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5514,7 +5434,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5751,11 +5671,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5763,7 +5679,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6004,11 +5920,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6016,7 +5928,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6257,11 +6169,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6269,7 +6177,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6510,11 +6418,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6522,7 +6426,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6763,11 +6667,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6775,7 +6675,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7016,11 +6916,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7028,7 +6924,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7265,11 +7161,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7277,7 +7169,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7518,11 +7410,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7530,7 +7418,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7771,11 +7659,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7783,7 +7667,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8024,11 +7908,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8036,7 +7916,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8277,11 +8157,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8289,7 +8165,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8530,11 +8406,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8542,7 +8414,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8783,11 +8655,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8795,7 +8663,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9036,11 +8904,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9048,7 +8912,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9289,11 +9153,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9301,7 +9161,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9542,11 +9402,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9554,7 +9410,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9795,11 +9651,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9807,7 +9659,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10048,11 +9900,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10060,7 +9908,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10297,11 +10145,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10309,7 +10153,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10550,11 +10394,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10562,7 +10402,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10803,11 +10643,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10815,7 +10651,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11056,11 +10892,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11068,7 +10900,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11305,11 +11137,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11317,7 +11145,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11558,11 +11386,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11570,7 +11394,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11811,11 +11635,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11823,7 +11643,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12064,11 +11884,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12076,7 +11892,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12317,11 +12133,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12329,7 +12141,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12570,11 +12382,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12582,7 +12390,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12823,11 +12631,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12835,7 +12639,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13076,11 +12880,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13088,7 +12888,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13329,11 +13129,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13341,7 +13137,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13582,11 +13378,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13594,7 +13386,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13835,11 +13627,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13847,7 +13635,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14088,11 +13876,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14100,7 +13884,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14341,11 +14125,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14353,7 +14133,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14594,11 +14374,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14606,7 +14382,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14847,11 +14623,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14859,7 +14631,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15100,11 +14872,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15112,7 +14880,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15353,11 +15121,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15365,7 +15129,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15606,11 +15370,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15618,7 +15378,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15859,11 +15619,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15871,7 +15627,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16112,11 +15868,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16124,7 +15876,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16365,11 +16117,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16377,7 +16125,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16618,11 +16366,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16630,7 +16374,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16871,11 +16615,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16883,7 +16623,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17124,11 +16864,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17136,7 +16872,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17377,11 +17113,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17389,7 +17121,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17630,11 +17362,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17642,7 +17370,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17883,11 +17611,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17895,7 +17619,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18136,11 +17860,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18148,7 +17868,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18389,11 +18109,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18401,7 +18117,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18642,11 +18358,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18654,7 +18366,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18895,11 +18607,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18907,7 +18615,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19148,11 +18856,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19160,7 +18864,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19393,11 +19097,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19405,7 +19105,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19642,11 +19342,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19654,7 +19350,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19887,11 +19583,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19899,7 +19591,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20140,11 +19832,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -20152,7 +19840,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
